--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488102_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488102_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>W. EL OTMANI MOHAMED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.285299999999999</v>
+        <v>7.2732</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6744</v>
+        <v>7.7258</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6109</v>
+        <v>-0.4525</v>
       </c>
       <c r="G2" t="n">
-        <v>7.3707</v>
+        <v>6.1955</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6693</v>
+        <v>-0.405</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7013</v>
+        <v>6.6005</v>
       </c>
       <c r="J2" t="n">
-        <v>9.0997</v>
+        <v>7.183</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8721</v>
+        <v>0.9956</v>
       </c>
       <c r="L2" t="n">
-        <v>6.2275</v>
+        <v>6.1874</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.729</v>
+        <v>-0.9875</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2028</v>
+        <v>-1.4007</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5262</v>
+        <v>0.4132</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.7929</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1716</v>
+        <v>0.5947</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8483</v>
+        <v>0.2671</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4134</v>
+        <v>0.3268</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4349</v>
+        <v>-0.0597</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1408</v>
+        <v>1.2071</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1258</v>
+        <v>1.2071</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. EL OTMANI MOHAMED</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.3656</v>
+        <v>6.9224</v>
       </c>
       <c r="E3" t="n">
-        <v>8.0709</v>
+        <v>5.452</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7052</v>
+        <v>1.4705</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1955</v>
+        <v>7.3707</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.405</v>
+        <v>1.6693</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6005</v>
+        <v>5.7013</v>
       </c>
       <c r="J3" t="n">
-        <v>7.183</v>
+        <v>9.0997</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9956</v>
+        <v>2.8721</v>
       </c>
       <c r="L3" t="n">
-        <v>6.1874</v>
+        <v>6.2275</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9875</v>
+        <v>-1.729</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4007</v>
+        <v>-1.2028</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4132</v>
+        <v>-0.5262</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5947</v>
+        <v>3.1716</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3595</v>
+        <v>0.4855</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.191</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3124</v>
+        <v>0.2945</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2071</v>
+        <v>-0.1408</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2071</v>
+        <v>0.1258</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3446</v>
+        <v>5.7064</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4478</v>
+        <v>3.7534</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8969</v>
+        <v>1.953</v>
       </c>
       <c r="G4" t="n">
         <v>0.462</v>
@@ -766,13 +766,13 @@
         <v>3.568</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6417</v>
+        <v>-0.2799</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.624</v>
+        <v>-0.3184</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0177</v>
+        <v>0.0384</v>
       </c>
       <c r="V4" t="n">
         <v>2.9474</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0623</v>
+        <v>4.554</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0899</v>
+        <v>3.4973</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9724</v>
+        <v>1.0566</v>
       </c>
       <c r="G5" t="n">
         <v>0.8762</v>
@@ -844,13 +844,13 @@
         <v>3.7662</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1332</v>
+        <v>-0.6415</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0608</v>
+        <v>-0.6533</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07240000000000001</v>
+        <v>0.0118</v>
       </c>
       <c r="V5" t="n">
         <v>1.5441</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5706</v>
+        <v>4.5426</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2133</v>
+        <v>4.9888</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6428</v>
+        <v>-0.4462</v>
       </c>
       <c r="G6" t="n">
         <v>1.4086</v>
@@ -922,13 +922,13 @@
         <v>1.5858</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2345</v>
+        <v>-0.2624</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0608</v>
+        <v>-0.2853</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1737</v>
+        <v>0.0228</v>
       </c>
       <c r="V6" t="n">
         <v>1.8107</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6717</v>
+        <v>2.2891</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5002</v>
+        <v>1.3983</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1716</v>
+        <v>0.8908</v>
       </c>
       <c r="G7" t="n">
         <v>0.3071</v>
@@ -1000,13 +1000,13 @@
         <v>2.3787</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9067</v>
+        <v>0.524</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1176</v>
+        <v>0.0157</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7891</v>
+        <v>0.5083</v>
       </c>
       <c r="V7" t="n">
         <v>0.0704</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2637</v>
+        <v>1.2022</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5202</v>
+        <v>0.7677</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.4346</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1778</v>
@@ -1078,13 +1078,13 @@
         <v>2.5769</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5891</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1638</v>
+        <v>0.4113</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4253</v>
+        <v>0.1164</v>
       </c>
       <c r="V8" t="n">
         <v>0.2666</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1301</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0905</v>
+        <v>2.3566</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9604</v>
+        <v>-1.6515</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5097</v>
@@ -1156,13 +1156,13 @@
         <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3336</v>
+        <v>0.2414</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.132</v>
+        <v>0.1341</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2016</v>
+        <v>0.1073</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2071</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1628</v>
+        <v>-2.3211</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.222</v>
+        <v>-2.6503</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0592</v>
+        <v>0.3292</v>
       </c>
       <c r="G10" t="n">
         <v>-2.217</v>
@@ -1234,13 +1234,13 @@
         <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1335</v>
+        <v>-0.0248</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1232</v>
+        <v>-0.5514</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2566</v>
+        <v>0.5266</v>
       </c>
       <c r="V10" t="n">
         <v>-0.674</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9137</v>
+        <v>-2.4572</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2832</v>
+        <v>-3.0795</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3696</v>
+        <v>0.6223</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6513</v>
@@ -1312,13 +1312,13 @@
         <v>0.7929</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7272</v>
+        <v>-0.2707</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.624</v>
+        <v>-0.4202</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1032</v>
+        <v>0.1495</v>
       </c>
       <c r="V11" t="n">
         <v>-0.337</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>28.6174</v>
+        <v>28.4167</v>
       </c>
       <c r="E12" t="n">
-        <v>24.102</v>
+        <v>24.2101</v>
       </c>
       <c r="F12" t="n">
-        <v>4.5156</v>
+        <v>4.2068</v>
       </c>
       <c r="G12" t="n">
         <v>11.0643</v>
@@ -1390,13 +1390,13 @@
         <v>22.2011</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7669000000000002</v>
+        <v>0.5663999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2581</v>
+        <v>-1.1497</v>
       </c>
       <c r="U12" t="n">
-        <v>2.0249</v>
+        <v>1.7159</v>
       </c>
       <c r="V12" t="n">
         <v>5.4874</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5906</v>
+        <v>2.3246</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5484</v>
+        <v>4.0577</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9578</v>
+        <v>-1.7332</v>
       </c>
       <c r="G14" t="n">
         <v>2.6724</v>
@@ -1546,13 +1546,13 @@
         <v>1.5858</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2981</v>
+        <v>0.4359</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8001</v>
+        <v>-0.2908</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5021</v>
+        <v>0.7267</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3873</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0115</v>
+        <v>0.6883</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0838</v>
+        <v>2.6763</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0722</v>
+        <v>-1.988</v>
       </c>
       <c r="G15" t="n">
         <v>0.0046</v>
@@ -1624,13 +1624,13 @@
         <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6105</v>
+        <v>0.2873</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5471</v>
+        <v>0.1396</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0634</v>
+        <v>0.1476</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>A. MIR AMATE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9624</v>
+        <v>-1.0987</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.7459</v>
+        <v>-0.7658</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7835</v>
+        <v>-0.3329</v>
       </c>
       <c r="G16" t="n">
-        <v>0.305</v>
+        <v>-0.7743</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3745</v>
+        <v>-0.2367</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0695</v>
+        <v>-0.5376</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9321</v>
+        <v>-0.652</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1659</v>
+        <v>0.0271</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2338</v>
+        <v>-0.6791</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6271</v>
+        <v>-0.1223</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7914</v>
+        <v>-0.2638</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1643</v>
+        <v>0.1415</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1716</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9822</v>
+        <v>0.3964</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4551</v>
+        <v>-0.4543</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5064</v>
+        <v>-0.1138</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9615</v>
+        <v>-0.3405</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5331</v>
+        <v>-0.2666</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5331</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MIR AMATE</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.183</v>
+        <v>-1.4221</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7658</v>
+        <v>-2.644</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4172</v>
+        <v>1.2219</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7743</v>
+        <v>0.305</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2367</v>
+        <v>1.3745</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5376</v>
+        <v>-1.0695</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.652</v>
+        <v>0.9321</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0271</v>
+        <v>2.1659</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6791</v>
+        <v>-1.2338</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1223</v>
+        <v>-0.6271</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2638</v>
+        <v>-0.7914</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1415</v>
+        <v>0.1643</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3964</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3964</v>
+        <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5385</v>
+        <v>-0.0047</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1138</v>
+        <v>-0.4045</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4247</v>
+        <v>0.3999</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2666</v>
+        <v>-0.5331</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2666</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.3696</v>
+        <v>-3.4819</v>
       </c>
       <c r="E18" t="n">
         <v>1.0067</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.3764</v>
+        <v>-4.4887</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2314</v>
@@ -1858,13 +1858,13 @@
         <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1123</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3816</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4939</v>
+        <v>0.3816</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0612</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>H. TAVIO SOLIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.9394</v>
+        <v>-3.7795</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3629</v>
+        <v>0.7141</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5765</v>
+        <v>-4.4936</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.1494</v>
+        <v>-1.7021</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1841</v>
+        <v>-2.1039</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.3335</v>
+        <v>0.4018</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4466</v>
+        <v>2.0376</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0454</v>
+        <v>-0.4975</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5988</v>
+        <v>2.5351</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.596</v>
+        <v>-3.7397</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8613</v>
+        <v>-1.6064</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.7347</v>
+        <v>-2.1333</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.5769</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1716</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5112</v>
+        <v>0.3368</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3621</v>
+        <v>0.0047</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1491</v>
+        <v>0.3322</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-2.4142</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. TAVIO SOLIS</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3659</v>
+        <v>-5.6953</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4085</v>
+        <v>-1.5853</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.7744</v>
+        <v>-4.11</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7021</v>
+        <v>-3.1494</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1039</v>
+        <v>1.1841</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4018</v>
+        <v>-4.3335</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0376</v>
+        <v>1.4466</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4975</v>
+        <v>2.0454</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5351</v>
+        <v>-0.5988</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.7397</v>
+        <v>-4.596</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6064</v>
+        <v>-0.8613</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1333</v>
+        <v>-3.7347</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>-3.1716</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2496</v>
+        <v>0.7552</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.301</v>
+        <v>0.1396</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0514</v>
+        <v>0.6156</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4142</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.0772</v>
+        <v>-0.7243000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. GARCIA GAZQUEZ</t>
+          <t>G. LOPEZ TORRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.141</v>
+        <v>-6.21</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.8193</v>
+        <v>-3.2572</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3217</v>
+        <v>-2.9528</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.461</v>
+        <v>-1.4481</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6422</v>
+        <v>-0.1816</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1033</v>
+        <v>-1.2665</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2505</v>
+        <v>1.2862</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3677</v>
+        <v>1.3588</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1172</v>
+        <v>-0.0726</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7115</v>
+        <v>-2.7343</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7255</v>
+        <v>-1.5404</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9861</v>
+        <v>-1.1939</v>
       </c>
       <c r="P21" t="n">
-        <v>-5.5503</v>
+        <v>-3.568</v>
       </c>
       <c r="Q21" t="n">
-        <v>-7.136</v>
+        <v>-4.1627</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1963</v>
+        <v>-0.2735</v>
       </c>
       <c r="T21" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.3808</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1301</v>
+        <v>0.1073</v>
       </c>
       <c r="V21" t="n">
-        <v>0.674</v>
+        <v>-0.9204</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.674</v>
+        <v>-0.9204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. LOPEZ TORRE</t>
+          <t>D. GARCIA GAZQUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.8245</v>
+        <v>-6.2814</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5628</v>
+        <v>-5.8193</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2617</v>
+        <v>-0.462</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4481</v>
+        <v>-1.461</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1816</v>
+        <v>1.6422</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2665</v>
+        <v>-3.1033</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2862</v>
+        <v>1.2505</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3588</v>
+        <v>2.3677</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0726</v>
+        <v>-1.1172</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7343</v>
+        <v>-2.7115</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5404</v>
+        <v>-0.7255</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1939</v>
+        <v>-1.9861</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.568</v>
+        <v>-5.5503</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.1627</v>
+        <v>-7.136</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8879</v>
+        <v>0.0559</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6864</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2016</v>
+        <v>-0.0103</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9204</v>
+        <v>0.674</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9204</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.598000000000001</v>
+        <v>-7.8255</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2972</v>
+        <v>-3.8897</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.3008</v>
+        <v>-3.9357</v>
       </c>
       <c r="G23" t="n">
         <v>-5.9001</v>
@@ -2248,13 +2248,13 @@
         <v>0.7929</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6544</v>
+        <v>-0.8819</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8736</v>
+        <v>-0.4661</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7809</v>
+        <v>-0.4158</v>
       </c>
       <c r="V23" t="n">
         <v>0.1459</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-29.7657</v>
+        <v>-29.7655</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.4905</v>
+        <v>-6.490500000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-23.2752</v>
+        <v>-23.275</v>
       </c>
       <c r="G24" t="n">
         <v>-9.668400000000002</v>
@@ -2326,7 +2326,7 @@
         <v>10.9023</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2568999999999997</v>
+        <v>0.2567000000000003</v>
       </c>
       <c r="T24" t="n">
         <v>-1.6875</v>
